--- a/data/nifty_options/nifty_options_2026-04.xlsx
+++ b/data/nifty_options/nifty_options_2026-04.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1607,6 +1607,240 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>10:00:21</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>TRADEABLE</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>24272.3</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>HARD VETO: CPR TRENDING DAY: Price 24272.30 above TC 24225.32 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>CPR TRENDING DAY: Price 24272.30 above TC 24225.32 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10:00:31</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>TRADEABLE</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>24231.6</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>HARD VETO: CPR TRENDING DAY: Price 24231.60 above TC 24215.12 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>CPR TRENDING DAY: Price 24231.60 above TC 24215.12 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nifty_options/nifty_options_2026-04.xlsx
+++ b/data/nifty_options/nifty_options_2026-04.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1841,6 +1841,240 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>10:00:21</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>TRADEABLE</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>24288.45</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>HARD VETO: CPR TRENDING DAY: Price 24288.45 below BC 24434.43 - BEARISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>CPR TRENDING DAY: Price 24288.45 below BC 24434.43 - BEARISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>10:00:27</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>TRADEABLE</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>23956.9</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>HARD VETO: CPR TRENDING DAY: Price 23956.90 below BC 24222.50 - BEARISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>CPR TRENDING DAY: Price 23956.90 below BC 24222.50 - BEARISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nifty_options/nifty_options_2026-04.xlsx
+++ b/data/nifty_options/nifty_options_2026-04.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2075,474 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>10:00:31</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>TRADEABLE</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>24101.3</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>HARD VETO: CPR TRENDING DAY: Price 24101.30 above TC 23935.24 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>CPR TRENDING DAY: Price 24101.30 above TC 23935.24 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>10:00:20</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>TRADEABLE</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>24156.3</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>HARD VETO: CPR TRENDING DAY: Price 24156.30 above TC 24072.95 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>CPR TRENDING DAY: Price 24156.30 above TC 24072.95 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>10:00:20</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>TRADEABLE</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>24175.1</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>HARD VETO: CPR TRENDING DAY: Price 24175.10 above TC 24020.28 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>CPR TRENDING DAY: Price 24175.10 above TC 24020.28 - BULLISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>10:00:26</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>TRADEABLE</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>23878.85</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>HARD VETO: CPR TRENDING DAY: Price 23878.85 below BC 24197.33 - BEARISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>CPR TRENDING DAY: Price 23878.85 below BC 24197.33 - BEARISH TRENDING DAY likely</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
